--- a/Design/Excel/ET/Datas/Game/UnitConfig.xlsx
+++ b/Design/Excel/ET/Datas/Game/UnitConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0DC9008-FE94-4332-9385-D487687ABBA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FC5215E-B14E-4666-BBD5-424EBAB8D979}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4240" yWindow="2260" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5780" yWindow="3630" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="27">
   <si>
     <t>##var</t>
   </si>
@@ -108,6 +108,14 @@
   </si>
   <si>
     <t>带有强力攻击技能2</t>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>EntityId</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -126,12 +134,14 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -139,18 +149,21 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -500,21 +513,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="21.08984375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="12.7265625" style="2" customWidth="1"/>
-    <col min="3" max="4" width="12.6328125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="15.08984375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="9.6328125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="28.7265625" style="2" customWidth="1"/>
-    <col min="8" max="9" width="11.7265625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="6.7265625" style="2" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="2"/>
+    <col min="2" max="3" width="12.7265625" style="2" customWidth="1"/>
+    <col min="4" max="5" width="12.6328125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="15.08984375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="9.6328125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="28.7265625" style="2" customWidth="1"/>
+    <col min="9" max="10" width="11.7265625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="6.7265625" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -522,26 +535,29 @@
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="4"/>
+      <c r="F1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:10" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
@@ -549,105 +565,115 @@
         <v>9</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="E2" s="4"/>
       <c r="F2" s="4" t="s">
         <v>10</v>
       </c>
       <c r="G2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="I2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="J2" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:10" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="4"/>
+      <c r="D3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="I3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="J3" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="26" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="26" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="1">
         <v>1001</v>
       </c>
       <c r="C4" s="1">
+        <v>1000001</v>
+      </c>
+      <c r="D4" s="1">
         <v>1</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="G4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="1">
+      <c r="H4" s="1">
         <v>1</v>
       </c>
-      <c r="H4" s="1">
+      <c r="I4" s="1">
         <v>178</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4" s="1">
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="26" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="26" x14ac:dyDescent="0.35">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>2001</v>
       </c>
       <c r="C5" s="1">
+        <v>2000001</v>
+      </c>
+      <c r="D5" s="1">
         <v>2</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="G5" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="1">
+      <c r="H5" s="1">
         <v>2</v>
       </c>
-      <c r="H5" s="1">
+      <c r="I5" s="1">
         <v>278</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5" s="1">
         <v>78</v>
       </c>
     </row>

--- a/Design/Excel/ET/Datas/Game/UnitConfig.xlsx
+++ b/Design/Excel/ET/Datas/Game/UnitConfig.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FC5215E-B14E-4666-BBD5-424EBAB8D979}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8706DCE5-870A-4DB3-B3FD-15206E64DAAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5780" yWindow="3630" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2280" yWindow="2280" windowWidth="19200" windowHeight="9970" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
+    <sheet name="UnitConfig" sheetId="1" r:id="rId1"/>
+    <sheet name="HeroAttribute" sheetId="2" r:id="rId2"/>
+    <sheet name="MonsterAttribute" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="48">
   <si>
     <t>##var</t>
   </si>
@@ -115,6 +117,71 @@
   </si>
   <si>
     <t>EntityId</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>HP</t>
+  </si>
+  <si>
+    <t>CriticalProbability</t>
+  </si>
+  <si>
+    <t>Mode</t>
+  </si>
+  <si>
+    <t>MP</t>
+  </si>
+  <si>
+    <t>Attack</t>
+  </si>
+  <si>
+    <t>Armor</t>
+  </si>
+  <si>
+    <t>MoveSpeed</t>
+  </si>
+  <si>
+    <t>AttackSpeed</t>
+  </si>
+  <si>
+    <t>float</t>
+  </si>
+  <si>
+    <t>long</t>
+  </si>
+  <si>
+    <t>生命值</t>
+  </si>
+  <si>
+    <t>暴击率</t>
+  </si>
+  <si>
+    <t>心情</t>
+  </si>
+  <si>
+    <t>魔法值</t>
+  </si>
+  <si>
+    <t>攻击力</t>
+  </si>
+  <si>
+    <t>防御</t>
+  </si>
+  <si>
+    <t>移速</t>
+  </si>
+  <si>
+    <t>攻击速度</t>
+  </si>
+  <si>
+    <t>ConfigId</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>int#ref=DTUnitConfig</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -122,7 +189,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
+  </numFmts>
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -167,8 +237,40 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -181,8 +283,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -190,12 +302,33 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -208,10 +341,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="4">
+    <cellStyle name="差" xfId="3" builtinId="27"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="好" xfId="2" builtinId="26"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -682,4 +820,368 @@
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9213B3E2-D9FE-415D-8834-68A4E5709623}">
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.36328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.6328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="15" x14ac:dyDescent="0.35">
+      <c r="A4" s="2"/>
+      <c r="B4" s="1">
+        <v>1001</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1200</v>
+      </c>
+      <c r="E4" s="2">
+        <v>10</v>
+      </c>
+      <c r="F4" s="2">
+        <v>300</v>
+      </c>
+      <c r="G4" s="2">
+        <v>300</v>
+      </c>
+      <c r="H4" s="2">
+        <v>500</v>
+      </c>
+      <c r="I4" s="2">
+        <v>100</v>
+      </c>
+      <c r="J4" s="2">
+        <v>100</v>
+      </c>
+      <c r="K4" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="15" x14ac:dyDescent="0.35">
+      <c r="A5" s="2"/>
+      <c r="B5" s="1">
+        <v>1001</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1</v>
+      </c>
+      <c r="D5" s="2">
+        <v>1300</v>
+      </c>
+      <c r="E5" s="2">
+        <v>10</v>
+      </c>
+      <c r="F5" s="2">
+        <v>300</v>
+      </c>
+      <c r="G5" s="2">
+        <v>300</v>
+      </c>
+      <c r="H5" s="2">
+        <v>500</v>
+      </c>
+      <c r="I5" s="2">
+        <v>100</v>
+      </c>
+      <c r="J5" s="2">
+        <v>100</v>
+      </c>
+      <c r="K5" s="2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{577B627A-085A-4A3E-B14C-764C06383C5A}">
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:11" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="15" x14ac:dyDescent="0.35">
+      <c r="A4" s="2"/>
+      <c r="B4" s="1">
+        <v>2001</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2">
+        <v>2200</v>
+      </c>
+      <c r="E4" s="2">
+        <v>10</v>
+      </c>
+      <c r="F4" s="2">
+        <v>300</v>
+      </c>
+      <c r="G4" s="2">
+        <v>300</v>
+      </c>
+      <c r="H4" s="2">
+        <v>500</v>
+      </c>
+      <c r="I4" s="2">
+        <v>100</v>
+      </c>
+      <c r="J4" s="2">
+        <v>100</v>
+      </c>
+      <c r="K4" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="15" x14ac:dyDescent="0.35">
+      <c r="B5" s="1">
+        <v>2001</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1</v>
+      </c>
+      <c r="D5" s="2">
+        <v>2400</v>
+      </c>
+      <c r="E5" s="2">
+        <v>10</v>
+      </c>
+      <c r="F5" s="2">
+        <v>300</v>
+      </c>
+      <c r="G5" s="2">
+        <v>300</v>
+      </c>
+      <c r="H5" s="2">
+        <v>500</v>
+      </c>
+      <c r="I5" s="2">
+        <v>100</v>
+      </c>
+      <c r="J5" s="2">
+        <v>100</v>
+      </c>
+      <c r="K5" s="2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Design/Excel/ET/Datas/Game/UnitConfig.xlsx
+++ b/Design/Excel/ET/Datas/Game/UnitConfig.xlsx
@@ -8,95 +8,30 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFE3121B-5EB4-4AFC-8563-B99271AEE50F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ADDB496-F0B6-474A-A039-B18CB36C7E8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2280" yWindow="2280" windowWidth="19200" windowHeight="9970" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UnitConfig" sheetId="1" r:id="rId1"/>
-    <sheet name="HeroAttribute" sheetId="2" r:id="rId2"/>
-    <sheet name="MonsterAttribute" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
   <si>
     <t>##var</t>
   </si>
   <si>
-    <t>ConfigId</t>
-  </si>
-  <si>
-    <t>Level</t>
-  </si>
-  <si>
-    <t>HP</t>
-  </si>
-  <si>
-    <t>CriticalProbability</t>
-  </si>
-  <si>
-    <t>Mode</t>
-  </si>
-  <si>
-    <t>MP</t>
-  </si>
-  <si>
-    <t>Attack</t>
-  </si>
-  <si>
-    <t>Armor</t>
-  </si>
-  <si>
-    <t>MoveSpeed</t>
-  </si>
-  <si>
-    <t>AttackSpeed</t>
-  </si>
-  <si>
     <t>##type</t>
   </si>
   <si>
-    <t>int#ref=DTUnitConfig</t>
-  </si>
-  <si>
     <t>int</t>
   </si>
   <si>
-    <t>float</t>
-  </si>
-  <si>
-    <t>long</t>
-  </si>
-  <si>
     <t>##</t>
-  </si>
-  <si>
-    <t>生命值</t>
-  </si>
-  <si>
-    <t>暴击率</t>
-  </si>
-  <si>
-    <t>心情</t>
-  </si>
-  <si>
-    <t>魔法值</t>
-  </si>
-  <si>
-    <t>攻击力</t>
-  </si>
-  <si>
-    <t>防御</t>
-  </si>
-  <si>
-    <t>移速</t>
-  </si>
-  <si>
-    <t>攻击速度</t>
   </si>
   <si>
     <t>Id</t>
@@ -169,10 +104,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
-  </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -217,40 +149,8 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -263,18 +163,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -282,33 +172,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -321,15 +190,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="4">
-    <cellStyle name="差" xfId="3" builtinId="27"/>
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-    <cellStyle name="好" xfId="2" builtinId="26"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -651,89 +515,89 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="E1" s="4"/>
       <c r="F1" s="4" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="3" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="4" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="H2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="4" t="s">
-        <v>34</v>
-      </c>
       <c r="J2" s="4" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="3" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="26" customHeight="1" x14ac:dyDescent="0.35">
@@ -748,13 +612,13 @@
         <v>1</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="H4" s="1">
         <v>1</v>
@@ -778,13 +642,13 @@
         <v>2</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="H5" s="1">
         <v>2</v>
@@ -801,372 +665,4 @@
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K5"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.6328125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="K2" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="2"/>
-      <c r="B4" s="1">
-        <v>1001</v>
-      </c>
-      <c r="C4" s="1">
-        <v>0</v>
-      </c>
-      <c r="D4" s="2">
-        <v>1200</v>
-      </c>
-      <c r="E4" s="2">
-        <v>10</v>
-      </c>
-      <c r="F4" s="2">
-        <v>300</v>
-      </c>
-      <c r="G4" s="2">
-        <v>300</v>
-      </c>
-      <c r="H4" s="2">
-        <v>500</v>
-      </c>
-      <c r="I4" s="2">
-        <v>100</v>
-      </c>
-      <c r="J4" s="2">
-        <v>60000</v>
-      </c>
-      <c r="K4" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="2"/>
-      <c r="B5" s="1">
-        <v>1001</v>
-      </c>
-      <c r="C5" s="1">
-        <v>1</v>
-      </c>
-      <c r="D5" s="2">
-        <v>1300</v>
-      </c>
-      <c r="E5" s="2">
-        <v>10</v>
-      </c>
-      <c r="F5" s="2">
-        <v>300</v>
-      </c>
-      <c r="G5" s="2">
-        <v>300</v>
-      </c>
-      <c r="H5" s="2">
-        <v>500</v>
-      </c>
-      <c r="I5" s="2">
-        <v>100</v>
-      </c>
-      <c r="J5" s="2">
-        <v>60000</v>
-      </c>
-      <c r="K5" s="2">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:K5"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="10" max="10" width="11" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="K2" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="2"/>
-      <c r="B4" s="1">
-        <v>2001</v>
-      </c>
-      <c r="C4" s="1">
-        <v>0</v>
-      </c>
-      <c r="D4" s="2">
-        <v>2200</v>
-      </c>
-      <c r="E4" s="2">
-        <v>10</v>
-      </c>
-      <c r="F4" s="2">
-        <v>300</v>
-      </c>
-      <c r="G4" s="2">
-        <v>300</v>
-      </c>
-      <c r="H4" s="2">
-        <v>500</v>
-      </c>
-      <c r="I4" s="2">
-        <v>100</v>
-      </c>
-      <c r="J4" s="2">
-        <v>60000</v>
-      </c>
-      <c r="K4" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="1">
-        <v>2001</v>
-      </c>
-      <c r="C5" s="1">
-        <v>1</v>
-      </c>
-      <c r="D5" s="2">
-        <v>2400</v>
-      </c>
-      <c r="E5" s="2">
-        <v>10</v>
-      </c>
-      <c r="F5" s="2">
-        <v>300</v>
-      </c>
-      <c r="G5" s="2">
-        <v>300</v>
-      </c>
-      <c r="H5" s="2">
-        <v>500</v>
-      </c>
-      <c r="I5" s="2">
-        <v>100</v>
-      </c>
-      <c r="J5" s="2">
-        <v>60000</v>
-      </c>
-      <c r="K5" s="2">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Design/Excel/ET/Datas/Game/UnitConfig.xlsx
+++ b/Design/Excel/ET/Datas/Game/UnitConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ADDB496-F0B6-474A-A039-B18CB36C7E8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17839334-0EDE-44A8-9B08-959B9AC9A79D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="29">
   <si>
     <t>##var</t>
   </si>
@@ -61,12 +61,6 @@
     <t>string</t>
   </si>
   <si>
-    <t>int&amp;group=c</t>
-  </si>
-  <si>
-    <t>int&amp;group=s</t>
-  </si>
-  <si>
     <t>测试说明</t>
   </si>
   <si>
@@ -98,6 +92,26 @@
   </si>
   <si>
     <t>带有强力攻击技能2</t>
+  </si>
+  <si>
+    <t>Width</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>宽度</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shape</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>形状</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -495,7 +509,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="21.08984375" style="2" customWidth="1"/>
@@ -503,14 +517,17 @@
     <col min="4" max="5" width="12.6328125" style="2" customWidth="1"/>
     <col min="6" max="6" width="15.08984375" style="2" customWidth="1"/>
     <col min="7" max="7" width="9.6328125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="28.7265625" style="2" customWidth="1"/>
-    <col min="9" max="10" width="11.7265625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="6.7265625" style="2" customWidth="1"/>
-    <col min="12" max="12" width="9" style="2" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="2"/>
+    <col min="8" max="8" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8" style="2" customWidth="1"/>
+    <col min="10" max="10" width="6.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.7265625" style="2" customWidth="1"/>
+    <col min="14" max="14" width="9" style="2" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -534,13 +551,19 @@
         <v>9</v>
       </c>
       <c r="I1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -564,13 +587,19 @@
         <v>2</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>14</v>
+        <v>27</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
@@ -582,25 +611,31 @@
         <v>6</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="I3" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="K3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="L3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>20</v>
-      </c>
     </row>
-    <row r="4" spans="1:10" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="1">
         <v>1001</v>
@@ -612,25 +647,31 @@
         <v>1</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H4" s="1">
         <v>1</v>
       </c>
       <c r="I4" s="1">
-        <v>178</v>
+        <v>1</v>
       </c>
       <c r="J4" s="1">
+        <v>2</v>
+      </c>
+      <c r="K4" s="1">
+        <v>4</v>
+      </c>
+      <c r="L4" s="1">
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>2001</v>
@@ -642,21 +683,27 @@
         <v>2</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" s="5" t="s">
         <v>23</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>25</v>
       </c>
       <c r="H5" s="1">
         <v>2</v>
       </c>
       <c r="I5" s="1">
-        <v>278</v>
+        <v>1</v>
       </c>
       <c r="J5" s="1">
+        <v>2</v>
+      </c>
+      <c r="K5" s="1">
+        <v>4</v>
+      </c>
+      <c r="L5" s="1">
         <v>78</v>
       </c>
     </row>

--- a/Design/Excel/ET/Datas/Game/UnitConfig.xlsx
+++ b/Design/Excel/ET/Datas/Game/UnitConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17839334-0EDE-44A8-9B08-959B9AC9A79D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F7C8015-3364-48F0-BAB6-40063DC0B93B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4530" yWindow="450" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UnitConfig" sheetId="1" r:id="rId1"/>

--- a/Design/Excel/ET/Datas/Game/UnitConfig.xlsx
+++ b/Design/Excel/ET/Datas/Game/UnitConfig.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F7C8015-3364-48F0-BAB6-40063DC0B93B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C9769E6-8BF6-4AE6-B51A-B04251AA1F23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4530" yWindow="450" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -662,10 +662,10 @@
         <v>1</v>
       </c>
       <c r="J4" s="1">
+        <v>1</v>
+      </c>
+      <c r="K4" s="1">
         <v>2</v>
-      </c>
-      <c r="K4" s="1">
-        <v>4</v>
       </c>
       <c r="L4" s="1">
         <v>68</v>
@@ -698,10 +698,10 @@
         <v>1</v>
       </c>
       <c r="J5" s="1">
+        <v>1</v>
+      </c>
+      <c r="K5" s="1">
         <v>2</v>
-      </c>
-      <c r="K5" s="1">
-        <v>4</v>
       </c>
       <c r="L5" s="1">
         <v>78</v>

--- a/Design/Excel/ET/Datas/Game/UnitConfig.xlsx
+++ b/Design/Excel/ET/Datas/Game/UnitConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C9769E6-8BF6-4AE6-B51A-B04251AA1F23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0012F9ED-BC66-43E1-BBF5-48EAD4391A64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4530" yWindow="450" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="33">
   <si>
     <t>##var</t>
   </si>
@@ -111,6 +111,22 @@
   </si>
   <si>
     <t>形状</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1_0_0</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1_1_0</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -509,25 +525,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="21.08984375" style="2" customWidth="1"/>
     <col min="2" max="3" width="12.7265625" style="2" customWidth="1"/>
-    <col min="4" max="5" width="12.6328125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="15.08984375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="9.6328125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="8" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8" style="2" customWidth="1"/>
-    <col min="10" max="10" width="6.26953125" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.81640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.7265625" style="2" customWidth="1"/>
-    <col min="14" max="14" width="9" style="2" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="2"/>
+    <col min="4" max="6" width="12.6328125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="15.08984375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="9.6328125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8" style="2" customWidth="1"/>
+    <col min="11" max="11" width="6.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.7265625" style="2" customWidth="1"/>
+    <col min="15" max="15" width="9" style="2" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -540,30 +556,33 @@
       <c r="D1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4" t="s">
+      <c r="E1" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -576,18 +595,18 @@
       <c r="D2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4" t="s">
-        <v>12</v>
-      </c>
+      <c r="E2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" s="4"/>
       <c r="G2" s="4" t="s">
         <v>12</v>
       </c>
       <c r="H2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>2</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>27</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>27</v>
@@ -598,8 +617,11 @@
       <c r="L2" s="4" t="s">
         <v>27</v>
       </c>
+      <c r="M2" s="4" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="3" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
@@ -610,32 +632,33 @@
       <c r="D3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="4"/>
+      <c r="F3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="I3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="J3" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="K3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="L3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="M3" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="1">
         <v>1001</v>
@@ -647,16 +670,16 @@
         <v>1</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="H4" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="H4" s="1">
-        <v>1</v>
       </c>
       <c r="I4" s="1">
         <v>1</v>
@@ -665,13 +688,16 @@
         <v>1</v>
       </c>
       <c r="K4" s="1">
+        <v>1</v>
+      </c>
+      <c r="L4" s="1">
         <v>2</v>
       </c>
-      <c r="L4" s="1">
+      <c r="M4" s="1">
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>2001</v>
@@ -683,27 +709,30 @@
         <v>2</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="H5" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="H5" s="1">
+      <c r="I5" s="1">
         <v>2</v>
-      </c>
-      <c r="I5" s="1">
-        <v>1</v>
       </c>
       <c r="J5" s="1">
         <v>1</v>
       </c>
       <c r="K5" s="1">
+        <v>1</v>
+      </c>
+      <c r="L5" s="1">
         <v>2</v>
       </c>
-      <c r="L5" s="1">
+      <c r="M5" s="1">
         <v>78</v>
       </c>
     </row>

--- a/Design/Excel/ET/Datas/Game/UnitConfig.xlsx
+++ b/Design/Excel/ET/Datas/Game/UnitConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0012F9ED-BC66-43E1-BBF5-48EAD4391A64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC321E16-CE48-4701-994B-EB519CA72CE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4530" yWindow="450" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4870" yWindow="790" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UnitConfig" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="32">
   <si>
     <t>##var</t>
   </si>
@@ -114,19 +114,15 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>Head</t>
+    <t>HeadIcon</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>string</t>
+    <t>1_1_0</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>1_0_0</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>1_1_0</t>
+    <t>0_0_0</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -556,10 +552,10 @@
       <c r="D1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="4"/>
+      <c r="F1" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="F1" s="4"/>
       <c r="G1" s="4" t="s">
         <v>7</v>
       </c>
@@ -595,10 +591,10 @@
       <c r="D2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="G2" s="4" t="s">
         <v>12</v>
       </c>
@@ -632,10 +628,10 @@
       <c r="D3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>13</v>
       </c>
+      <c r="F3" s="4"/>
       <c r="G3" s="4" t="s">
         <v>14</v>
       </c>
@@ -670,10 +666,10 @@
         <v>1</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>19</v>
@@ -709,10 +705,10 @@
         <v>2</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>22</v>

--- a/Design/Excel/ET/Datas/Game/UnitConfig.xlsx
+++ b/Design/Excel/ET/Datas/Game/UnitConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC321E16-CE48-4701-994B-EB519CA72CE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E09C6FED-EA0D-4969-8488-22862BAAD806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4870" yWindow="790" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UnitConfig" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="29">
   <si>
     <t>##var</t>
   </si>
@@ -111,18 +111,6 @@
   </si>
   <si>
     <t>形状</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>HeadIcon</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>1_1_0</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>0_0_0</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -521,25 +509,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="21.08984375" style="2" customWidth="1"/>
     <col min="2" max="3" width="12.7265625" style="2" customWidth="1"/>
-    <col min="4" max="6" width="12.6328125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="15.08984375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="9.6328125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="8" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8" style="2" customWidth="1"/>
-    <col min="11" max="11" width="6.26953125" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.81640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.7265625" style="2" customWidth="1"/>
-    <col min="15" max="15" width="9" style="2" customWidth="1"/>
-    <col min="16" max="16384" width="9" style="2"/>
+    <col min="4" max="5" width="12.6328125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="15.08984375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="9.6328125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8" style="2" customWidth="1"/>
+    <col min="10" max="10" width="6.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.7265625" style="2" customWidth="1"/>
+    <col min="14" max="14" width="9" style="2" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -554,31 +542,28 @@
       </c>
       <c r="E1" s="4"/>
       <c r="F1" s="4" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -599,10 +584,10 @@
         <v>12</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>27</v>
@@ -613,11 +598,8 @@
       <c r="L2" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="M2" s="4" t="s">
-        <v>27</v>
-      </c>
     </row>
-    <row r="3" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
@@ -631,30 +613,29 @@
       <c r="E3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="4"/>
+      <c r="F3" s="4" t="s">
+        <v>14</v>
+      </c>
       <c r="G3" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="M3" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="1">
         <v>1001</v>
@@ -669,13 +650,13 @@
         <v>13</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="G4" s="5" t="s">
         <v>20</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1</v>
       </c>
       <c r="I4" s="1">
         <v>1</v>
@@ -684,16 +665,13 @@
         <v>1</v>
       </c>
       <c r="K4" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L4" s="1">
-        <v>2</v>
-      </c>
-      <c r="M4" s="1">
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>2001</v>
@@ -708,27 +686,24 @@
         <v>21</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="G5" s="5" t="s">
         <v>23</v>
       </c>
+      <c r="H5" s="1">
+        <v>2</v>
+      </c>
       <c r="I5" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J5" s="1">
         <v>1</v>
       </c>
       <c r="K5" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L5" s="1">
-        <v>2</v>
-      </c>
-      <c r="M5" s="1">
         <v>78</v>
       </c>
     </row>
